--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>El listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de Seguridad Social previsto en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
@@ -124,16 +124,16 @@
     <t/>
   </si>
   <si>
-    <t>9C6D289CC738F6E1D6F8E3F07E450321</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>29/07/2022</t>
+    <t>D36342BA4A92BCD2B3A9190A432D0FEC</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>14/07/2023</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
